--- a/artfynd/A 57846-2025 artfynd.xlsx
+++ b/artfynd/A 57846-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106699974</v>
+        <v>106699959</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra Målen, trädid F98080, Sm</t>
+          <t>Råsen, trädid F98094, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476021.0212687026</v>
+        <v>476034</v>
       </c>
       <c r="R2" t="n">
-        <v>6347426.961880559</v>
+        <v>6347495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>F98080</t>
+          <t>F98094</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,19 +752,14 @@
           <t>2014-11-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-11-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Biotopskydd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106699959</v>
+        <v>106699960</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,14 +825,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råsen, trädid F98094, Sm</t>
+          <t>Råsen, trädid F98093, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476033.882292551</v>
+        <v>476023</v>
       </c>
       <c r="R3" t="n">
-        <v>6347495.556192532</v>
+        <v>6347498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +859,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>F98094</t>
+          <t>F98093</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -882,19 +867,9 @@
           <t>2014-11-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-11-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106699960</v>
+        <v>106699961</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,14 +940,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råsen, trädid F98093, Sm</t>
+          <t>Råsen, trädid F98092, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476023.0631522958</v>
+        <v>476007</v>
       </c>
       <c r="R4" t="n">
-        <v>6347498.322829407</v>
+        <v>6347508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +974,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>F98093</t>
+          <t>F98092</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1012,19 +982,9 @@
           <t>2014-11-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-11-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1053,6 +1013,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106699974</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norra Målen, trädid F98080, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>476021</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6347427</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stockaryd</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>F98080</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/A 57846-2025 artfynd.xlsx
+++ b/artfynd/A 57846-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106699959</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106699960</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106699961</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,8 +1147,19 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106699974</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>